--- a/database/controller_excel/Resguardo_Miguel_Ángel_Vera_Pérez.xlsx
+++ b/database/controller_excel/Resguardo_Miguel_Ángel_Vera_Pérez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -102,6 +102,15 @@
   </si>
   <si>
     <t>48DT7V1</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>Access PRO</t>
+  </si>
+  <si>
+    <t>HP</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -804,7 +813,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1069,86 +1078,115 @@
       <c r="J18" s="53"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A19" s="18"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="18"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+    <row r="19" spans="1:11">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53">
+        <v>3</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="53">
+        <v>12345678</v>
+      </c>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53">
+        <v>12345678</v>
+      </c>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53">
+        <v>4</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="53">
+        <v>1234</v>
+      </c>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53">
+        <v>12345</v>
+      </c>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>5</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="53">
+        <v>12345</v>
+      </c>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53">
+        <v>1234591</v>
+      </c>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="19"/>
-      <c r="B22" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="9">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="31"/>
+    </row>
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A23" s="18"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="31"/>
     </row>
     <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="20"/>
-      <c r="B24" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
-        <v>31</v>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="19"/>
+      <c r="B25" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1159,21 +1197,19 @@
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
     </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
+    <row r="26" spans="1:11" customHeight="1" ht="9">
       <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15.75">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
         <v>33</v>
@@ -1201,9 +1237,11 @@
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
     </row>
-    <row r="29" spans="1:11" customHeight="1" ht="12">
-      <c r="A29" s="21"/>
-      <c r="B29" s="28"/>
+    <row r="29" spans="1:11" customHeight="1" ht="15">
+      <c r="A29" s="20"/>
+      <c r="B29" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
@@ -1213,10 +1251,10 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A30" s="17"/>
-      <c r="B30" s="29" t="s">
-        <v>35</v>
+    <row r="30" spans="1:11" customHeight="1" ht="15">
+      <c r="A30" s="20"/>
+      <c r="B30" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1227,84 +1265,124 @@
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="25" t="s">
-        <v>36</v>
-      </c>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+    </row>
+    <row r="32" spans="1:11" customHeight="1" ht="12">
+      <c r="A32" s="21"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A33" s="17"/>
+      <c r="B33" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="26"/>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
-      <c r="H33" s="34" t="s">
-        <v>37</v>
-      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
     </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="34" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+    </row>
     <row r="35" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="H37" s="25" t="str">
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="H36" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+    </row>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="38" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+    </row>
+    <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C40" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="H40" s="25" t="str">
         <f>C8</f>
         <v>Miguel Ángel Vera Pérez</v>
       </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="H38" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+    </row>
     <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="C41" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="H41" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+    </row>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1319,33 +1397,42 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I17:J21"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Miguel_Ángel_Vera_Pérez.xlsx
+++ b/database/controller_excel/Resguardo_Miguel_Ángel_Vera_Pérez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>01/07/2025</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>ssd</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
+    <t>ds</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -83,34 +83,16 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>SERVIDOR 18</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>POWEREDGE R720</t>
-  </si>
-  <si>
-    <t>B3X7RV1</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>POWERVAULT MD3200i</t>
-  </si>
-  <si>
-    <t>48DT7V1</t>
-  </si>
-  <si>
-    <t>ACCESSPOINT</t>
-  </si>
-  <si>
-    <t>Access PRO</t>
-  </si>
-  <si>
-    <t>HP</t>
+    <t>Teléfono Celular</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>Samsung12</t>
+  </si>
+  <si>
+    <t>Linea: 99</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -419,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -537,6 +519,9 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -813,7 +798,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1047,146 +1032,110 @@
         <v>24</v>
       </c>
       <c r="F17" s="53"/>
-      <c r="G17" s="53" t="s">
-        <v>25</v>
+      <c r="G17" s="53">
+        <v>1</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
+    <row r="18" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A18" s="18"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A19" s="18"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="31"/>
+    </row>
+    <row r="20" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A21" s="19"/>
+      <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="53" t="s">
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+    </row>
+    <row r="22" spans="1:11" customHeight="1" ht="9">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A23" s="20"/>
+      <c r="B23" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:11" customHeight="1" ht="15">
+      <c r="A24" s="20"/>
+      <c r="B24" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="52"/>
-      <c r="B19" s="53">
-        <v>3</v>
-      </c>
-      <c r="C19" s="53" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15">
+      <c r="A25" s="20"/>
+      <c r="B25" s="27" t="s">
         <v>29</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="53">
-        <v>12345678</v>
-      </c>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53">
-        <v>12345678</v>
-      </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="52"/>
-      <c r="B20" s="53">
-        <v>4</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="53">
-        <v>1234</v>
-      </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53">
-        <v>12345</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53">
-        <v>5</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="53">
-        <v>12345</v>
-      </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53">
-        <v>1234591</v>
-      </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="18"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="31"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="18"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="31"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="19"/>
-      <c r="B25" s="33" t="s">
-        <v>32</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1197,22 +1146,24 @@
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
     </row>
-    <row r="26" spans="1:11" customHeight="1" ht="9">
+    <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
+      <c r="B26" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1223,11 +1174,9 @@
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
     </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="27" t="s">
-        <v>34</v>
-      </c>
+    <row r="28" spans="1:11" customHeight="1" ht="12">
+      <c r="A28" s="21"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
@@ -1237,10 +1186,10 @@
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
     </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15">
-      <c r="A29" s="20"/>
-      <c r="B29" s="27" t="s">
-        <v>35</v>
+    <row r="29" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A29" s="17"/>
+      <c r="B29" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1251,138 +1200,84 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15">
-      <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15">
-      <c r="A31" s="20"/>
-      <c r="B31" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="12">
-      <c r="A32" s="21"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="26"/>
+    <row r="30" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="25" t="s">
+        <v>33</v>
+      </c>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
+      <c r="H32" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A33" s="17"/>
-      <c r="B33" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-    </row>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
       <c r="C36" s="25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
-      <c r="H36" s="34" t="s">
-        <v>40</v>
+      <c r="H36" s="25" t="str">
+        <f>C8</f>
+        <v>Miguel Ángel Vera Pérez</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="H37" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C40" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="H40" s="25" t="str">
-        <f>C8</f>
-        <v>Miguel Ángel Vera Pérez</v>
-      </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C41" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="H41" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1397,42 +1292,29 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I17:J21"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
